--- a/out/global_metric/excel/vgg.xlsx
+++ b/out/global_metric/excel/vgg.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,15 +449,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -468,20 +488,32 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9404761791229248</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8230158631256616</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9365079313903756</v>
+      </c>
+      <c r="D2" t="n">
+        <v>58</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -492,20 +524,32 @@
         <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9345238095238096</v>
+        <v>0.9583333134651184</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7489795832252996</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.955694528278204</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>101</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -516,20 +560,32 @@
         <v>53</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.9642857313156128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7931972696093295</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9623599650072854</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -540,20 +596,32 @@
         <v>72</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9285714285714284</v>
+        <v>0.9226190447807312</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7079364997195767</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9154242291102376</v>
+      </c>
+      <c r="D5" t="n">
+        <v>53</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -564,140 +632,32 @@
         <v>91</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9642857313156128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8650793547156087</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9621394179557704</v>
+      </c>
+      <c r="D6" t="n">
+        <v>61</v>
       </c>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9404761904761904</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.7823129158681569</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>129</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9464285714285714</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8222222124457673</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>148</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8928571428571428</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6753968170522487</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>167</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9345238095238094</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7793650701957674</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>186</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9226190476190474</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7269841188842593</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -714,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,15 +695,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -754,20 +734,32 @@
         <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9583333333333331</v>
+        <v>0.9523809552192688</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8357142756309526</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9495192256497608</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -778,20 +770,32 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9226190447807312</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7045351391591622</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9195135382904196</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61</v>
       </c>
       <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>94</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -802,20 +806,32 @@
         <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.9583333134651184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6331065681877335</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9559599993740974</v>
+      </c>
+      <c r="D4" t="n">
+        <v>61</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -826,20 +842,32 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9226190476190474</v>
+        <v>0.9345238208770752</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7172335521009612</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9299336441731624</v>
+      </c>
+      <c r="D5" t="n">
+        <v>57</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -850,140 +878,32 @@
         <v>92</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9702380952380952</v>
+        <v>0.9642857313156128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8807256131512256</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9625668398031512</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.7269841186759257</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9404761904761904</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8283446614528128</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>149</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7547618961130953</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>168</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9226190476190476</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7886621219223896</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>187</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8988095238095239</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6706349127645506</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1000,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,15 +941,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -1040,20 +980,32 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9404761904761904</v>
+        <v>0.9464285969734192</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8111111012804233</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.943035823536655</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1064,20 +1016,32 @@
         <v>36</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.851190447807312</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7648525988866752</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.8285924122618276</v>
+      </c>
+      <c r="D3" t="n">
+        <v>41</v>
       </c>
       <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1088,20 +1052,32 @@
         <v>55</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9345238095238096</v>
+        <v>0.9345238208770752</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7442176783721252</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9318960700743441</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62</v>
       </c>
       <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>95</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1112,20 +1088,32 @@
         <v>74</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7140589489051939</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.900694541962565</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
       </c>
       <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1136,140 +1124,32 @@
         <v>93</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857142857144</v>
+        <v>0.9642857313156128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8722222118167989</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9625668398031512</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6860544136668691</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>131</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9583333333333331</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8238095141230162</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>150</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9107142857142856</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7698412608465609</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>169</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9345238095238096</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7769841179675926</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>188</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9226190476190474</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7212018059071779</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1286,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,15 +1187,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -1326,20 +1226,32 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9404761904761902</v>
+        <v>0.9404761791229248</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8301587201375663</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9356519023495328</v>
+      </c>
+      <c r="D2" t="n">
+        <v>56</v>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>102</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1350,20 +1262,32 @@
         <v>37</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9404761904761904</v>
+        <v>0.9166666865348816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7807256145083686</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9105295140601426</v>
+      </c>
+      <c r="D3" t="n">
+        <v>55</v>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>99</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1374,20 +1298,32 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9464285714285716</v>
+        <v>0.886904776096344</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7614512382468959</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.8733283016195618</v>
+      </c>
+      <c r="D4" t="n">
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1398,20 +1334,32 @@
         <v>75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9404761904761904</v>
+        <v>0.9226190447807312</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7158730076296296</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9182114318024264</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58</v>
       </c>
       <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>97</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1422,140 +1370,32 @@
         <v>94</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857142857144</v>
+        <v>0.9464285969734192</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8807256131115431</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
+        <v>0.9439979207369784</v>
+      </c>
+      <c r="D6" t="n">
+        <v>62</v>
       </c>
       <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>97</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>113</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8809523809523809</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.618820854609559</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>132</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8988095238095238</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6910430754680247</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>151</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8869047619047619</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7626984040628306</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>170</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9523809523809524</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8039682443478837</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>189</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7410430754739771</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vgg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>19</t>
         </is>

--- a/out/global_metric/excel/vgg.xlsx
+++ b/out/global_metric/excel/vgg.xlsx
@@ -498,25 +498,29 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.8488964438438416</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9356519023495328</v>
+        <v>0.8481241819598737</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>229</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>271</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.922587340020754</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9127766310938584</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -536,25 +540,29 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.8149405717849731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9372666117619016</v>
+        <v>0.8125873872091214</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>207</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>273</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9093047388446904</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8940005532917165</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -574,25 +582,29 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9583333134651184</v>
+        <v>0.8913412690162659</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9559599993740974</v>
+        <v>0.8912280651509316</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>272</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.942972443214574</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9293205301653932</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -612,25 +624,29 @@
         <v>86</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.8675721287727356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9299336441731624</v>
+        <v>0.8674617411488401</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9235097428802028</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9048976170920076</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -650,25 +666,29 @@
         <v>109</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.8471986651420593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9621394179557704</v>
+        <v>0.8471241644092686</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>243</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9108151735270378</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8965196648776869</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -764,25 +784,29 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.8302206993103027</v>
       </c>
       <c r="C2" t="n">
-        <v>0.928964054088371</v>
+        <v>0.8301967246016992</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9056151274068948</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9016546880219276</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -802,25 +826,29 @@
         <v>41</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9047619104385376</v>
+        <v>0.8370118737220764</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9016249400122244</v>
+        <v>0.8362941467007543</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>227</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9082324455205812</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8903092406211216</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -840,25 +868,29 @@
         <v>64</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9583333134651184</v>
+        <v>0.8421052694320679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9562092668988592</v>
+        <v>0.8418846666509425</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>237</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>259</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9179637956877666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9135065775300744</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -878,25 +910,29 @@
         <v>87</v>
       </c>
       <c r="B5" t="n">
-        <v>0.898809552192688</v>
+        <v>0.8183361887931824</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8866621640724526</v>
+        <v>0.8150934268197254</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G5" t="n">
-        <v>103</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>280</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8948460740228296</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8773881511908118</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -916,25 +952,29 @@
         <v>110</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.8251273632049561</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9619047567837744</v>
+        <v>0.8250950629694684</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>247</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8989046466044044</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8821534107048867</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1030,25 +1070,29 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.7945670485496521</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9498132883845936</v>
+        <v>0.7933063565693479</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>99</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8809985010953534</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8683289553414313</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1068,25 +1112,29 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.8268251419067383</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9311859937686472</v>
+        <v>0.8268246231283294</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9031534647757408</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8906688588723454</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1106,25 +1154,29 @@
         <v>65</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.8166383504867554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9318960700743441</v>
+        <v>0.8165193664137589</v>
       </c>
       <c r="D4" t="n">
+        <v>233</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="n">
         <v>62</v>
       </c>
-      <c r="E4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>95</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8995157384987893</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8748580724879238</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1144,25 +1196,29 @@
         <v>88</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8809523582458496</v>
+        <v>0.8166383504867554</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8788752653219356</v>
+        <v>0.8146503446760407</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>210</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>271</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8849302432837542</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8475578661339072</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1182,25 +1238,29 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.8132427930831909</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9619047567837744</v>
+        <v>0.8129575690572939</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.895722356739306</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8813495547477039</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1296,25 +1356,29 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.7962648272514343</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9492063440870748</v>
+        <v>0.796217270951278</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8604980975441024</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8468554703972284</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1334,25 +1398,29 @@
         <v>43</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.7928692698478699</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9111111059969766</v>
+        <v>0.7922939017961572</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8766920327453016</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8733938659275384</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1372,25 +1440,29 @@
         <v>66</v>
       </c>
       <c r="B4" t="n">
-        <v>0.898809552192688</v>
+        <v>0.8132427930831909</v>
       </c>
       <c r="C4" t="n">
-        <v>0.890217177291922</v>
+        <v>0.8125809910108348</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>222</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8804450593796841</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.854336821579347</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1410,25 +1482,29 @@
         <v>89</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9107142686843872</v>
+        <v>0.7996604442596436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9056285759452029</v>
+        <v>0.7994054440665871</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>96</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8783811829816672</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8516109036089736</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vgg</t>
@@ -1448,25 +1524,29 @@
         <v>112</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.8200339674949646</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9492063440870748</v>
+        <v>0.8186744838594804</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8747838118298168</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8439840821149187</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vgg</t>

--- a/out/global_metric/excel/vgg.xlsx
+++ b/out/global_metric/excel/vgg.xlsx
@@ -498,28 +498,28 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8488964438438416</v>
+        <v>0.8081493973731995</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8481241819598737</v>
+        <v>0.808069734317566</v>
       </c>
       <c r="D2" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="H2" t="n">
-        <v>0.922587340020754</v>
+        <v>0.8998385794995964</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9127766310938584</v>
+        <v>0.8869481849212721</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8149405717849731</v>
+        <v>0.8251273632049561</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8125873872091214</v>
+        <v>0.8245426757102374</v>
       </c>
       <c r="D3" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9093047388446904</v>
+        <v>0.9010434682347516</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8940005532917165</v>
+        <v>0.8745214651626133</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -582,28 +582,28 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8913412690162659</v>
+        <v>0.8268251419067383</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8912280651509316</v>
+        <v>0.8267846795536302</v>
       </c>
       <c r="D4" t="n">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.942972443214574</v>
+        <v>0.9012683039317422</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9293205301653932</v>
+        <v>0.8786697807633227</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -624,28 +624,28 @@
         <v>86</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8675721287727356</v>
+        <v>0.8081493973731995</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8674617411488401</v>
+        <v>0.8080940838558843</v>
       </c>
       <c r="D5" t="n">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9235097428802028</v>
+        <v>0.8812809869710596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9048976170920076</v>
+        <v>0.8494498873342399</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -666,28 +666,28 @@
         <v>109</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8471986651420593</v>
+        <v>0.8387096524238586</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8471241644092686</v>
+        <v>0.8378045372249956</v>
       </c>
       <c r="D6" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9108151735270378</v>
+        <v>0.9253141934739998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8965196648776869</v>
+        <v>0.9249542626546252</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -784,28 +784,28 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8302206993103027</v>
+        <v>0.8149405717849731</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8301967246016992</v>
+        <v>0.8137033236274961</v>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9056151274068948</v>
+        <v>0.8755909143318344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9016546880219276</v>
+        <v>0.8378285248406223</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -826,28 +826,28 @@
         <v>41</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8370118737220764</v>
+        <v>0.8217317461967468</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8362941467007543</v>
+        <v>0.8216988506976678</v>
       </c>
       <c r="D3" t="n">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9082324455205812</v>
+        <v>0.8912832929782083</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8903092406211216</v>
+        <v>0.8803711888270744</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -868,28 +868,28 @@
         <v>64</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8421052694320679</v>
+        <v>0.8234295248985291</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8418846666509425</v>
+        <v>0.8232047975638144</v>
       </c>
       <c r="D4" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9179637956877666</v>
+        <v>0.8972789115646258</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9135065775300744</v>
+        <v>0.8643967032001586</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
         <v>87</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8183361887931824</v>
+        <v>0.7945670485496521</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8150934268197254</v>
+        <v>0.7940327271026165</v>
       </c>
       <c r="D5" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8948460740228296</v>
+        <v>0.8862389023405972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8773881511908118</v>
+        <v>0.8670854983774542</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -952,28 +952,28 @@
         <v>110</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8251273632049561</v>
+        <v>0.7775891423225403</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8250950629694684</v>
+        <v>0.7725111028651358</v>
       </c>
       <c r="D6" t="n">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8989046466044044</v>
+        <v>0.8753314885276144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8821534107048867</v>
+        <v>0.8380685080103781</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1070,28 +1070,28 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7945670485496521</v>
+        <v>0.8081493973731995</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7933063565693479</v>
+        <v>0.807347517405739</v>
       </c>
       <c r="D2" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8809985010953534</v>
+        <v>0.9044448287789691</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8683289553414313</v>
+        <v>0.8918253703469499</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1112,28 +1112,28 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8268251419067383</v>
+        <v>0.8183361887931824</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8268246231283294</v>
+        <v>0.8183340633518106</v>
       </c>
       <c r="D3" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F3" t="n">
         <v>52</v>
       </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
       <c r="G3" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9031534647757408</v>
+        <v>0.9012279488066413</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8906688588723454</v>
+        <v>0.8847296419023405</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1154,28 +1154,28 @@
         <v>65</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8166383504867554</v>
+        <v>0.8098471760749817</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8165193664137589</v>
+        <v>0.809842260446223</v>
       </c>
       <c r="D4" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8995157384987893</v>
+        <v>0.8787501441254468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8748580724879238</v>
+        <v>0.8407354637522746</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         <v>88</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8166383504867554</v>
+        <v>0.8098471760749817</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8146503446760407</v>
+        <v>0.8096491177841876</v>
       </c>
       <c r="D5" t="n">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>271</v>
+        <v>229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8849302432837542</v>
+        <v>0.8886140897036781</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8475578661339072</v>
+        <v>0.8614271501205428</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1238,28 +1238,28 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8132427930831909</v>
+        <v>0.8353140950202942</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8129575690572939</v>
+        <v>0.8346965591868235</v>
       </c>
       <c r="D6" t="n">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="H6" t="n">
-        <v>0.895722356739306</v>
+        <v>0.8998039893923672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8813495547477039</v>
+        <v>0.8695598231307977</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1356,28 +1356,28 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7962648272514343</v>
+        <v>0.7996604442596436</v>
       </c>
       <c r="C2" t="n">
-        <v>0.796217270951278</v>
+        <v>0.7991735964636226</v>
       </c>
       <c r="D2" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8604980975441024</v>
+        <v>0.8804623544332988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8468554703972284</v>
+        <v>0.8526640501312185</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1398,28 +1398,28 @@
         <v>43</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7928692698478699</v>
+        <v>0.7894737124443054</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7922939017961572</v>
+        <v>0.7892057211404193</v>
       </c>
       <c r="D3" t="n">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8766920327453016</v>
+        <v>0.8882278335062838</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8733938659275384</v>
+        <v>0.8711537223818138</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1440,28 +1440,28 @@
         <v>66</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8132427930831909</v>
+        <v>0.8285229206085205</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8125809910108348</v>
+        <v>0.8281345197531272</v>
       </c>
       <c r="D4" t="n">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8804450593796841</v>
+        <v>0.9072062723394444</v>
       </c>
       <c r="I4" t="n">
-        <v>0.854336821579347</v>
+        <v>0.8829217926804022</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1482,28 +1482,28 @@
         <v>89</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7996604442596436</v>
+        <v>0.7894737124443054</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7994054440665871</v>
+        <v>0.789093718271713</v>
       </c>
       <c r="D5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E5" t="n">
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8783811829816672</v>
+        <v>0.882364810330912</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8516109036089736</v>
+        <v>0.8593837045028921</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1524,28 +1524,28 @@
         <v>112</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8200339674949646</v>
+        <v>0.8370118737220764</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8186744838594804</v>
+        <v>0.8370076510919199</v>
       </c>
       <c r="D6" t="n">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8747838118298168</v>
+        <v>0.9022944771128788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8439840821149187</v>
+        <v>0.8826771376081531</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
